--- a/Excel_Template.xlsx
+++ b/Excel_Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MP946KB\WORKDIR\files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\SOWautomation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAAB1241-42C7-4AC9-82E7-8DB9952F87BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0ED9D18-6783-44B4-AABD-268890B1A669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B035CEB9-D536-4B4E-883F-C55C1F3FCF2A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{B035CEB9-D536-4B4E-883F-C55C1F3FCF2A}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary master" sheetId="1" r:id="rId1"/>
@@ -690,9 +690,6 @@
     <t>CLIENT_ENV_TOOL</t>
   </si>
   <si>
-    <t>The Services under this SOW shall begin as of **COMMENCEMENT_DATE** (the “Commencement Date”) and end on the date that is *[ [XX] months after the Go-Live Date]* (the “Term”).   [NOTE TO DRAFT:  A typical structure might provide for a defined number of months for the Managed Services in relation to the Go-Live Date (or the last of the Go-Live Dates if there is more than one), so that here is a single, coordinated end of the Term for the Managed Services.]</t>
-  </si>
-  <si>
     <t>**1 Please answer 'Yes' or 'No'.                   **1a If appropriate consider limiting Section 9.a to “In connection with the Onboarding Services,…” if all Deliverables will occur during the Onboarding phase.               **1b fill the number of days.           **1c  Option 1: Fixed Price: EY’s correction efforts will be made at no additional charge. Option 2:T&amp;M: EY’s correction efforts will be made on a time and materials basis.           **1d fill the number of days.</t>
   </si>
   <si>
@@ -939,9 +936,6 @@
     <t>Those Service Levels for which no Service Level Credit is payable, but which are meaningful to Client’s business.  Key Measurements are identified in Attachment B-1 (Service Level Metrics).  [NOTE TO DRAFT:  Delete or modify, unless Service Level Credits will apply.]</t>
   </si>
   <si>
-    <t>The methodology used to determine the potential elimination of a Service Level Credit, as described in Section 5 of Schedule B (Service Level Methodology).  [NOTE TO DRAFT:  Delete, unless Service Level Credits will apply.]</t>
-  </si>
-  <si>
     <t>A Service Level Default of a Critical Service Level.  [NOTE TO DRAFT:  Delete, unless Service Level Credits will apply.]</t>
   </si>
   <si>
@@ -955,9 +949,6 @@
   </si>
   <si>
     <t>Maximum SLA Allocation Percentage</t>
-  </si>
-  <si>
-    <t>[Twenty-five (25)] percentage points, which would represent [twenty-five percent (25%)] of the At Risk Amount.  [NOTE TO DRAFT:  Delete, unless Service Level Credits will apply.]</t>
   </si>
   <si>
     <t>The time during, or frequency by, which a Service Level shall be measured. The Measurement Window will exclude scheduled maintenance and emergency maintenance</t>
@@ -1055,6 +1046,15 @@
   </si>
   <si>
     <t>tableA</t>
+  </si>
+  <si>
+    <t>The Services under this SOW shall begin as of **COMMENCEMENT_DATE** (the “Commencement Date”) and end on the date that is  [XX] months after the Go-Live Date (the “Term”).   [NOTE TO DRAFT:  A typical structure might provide for a defined number of months for the Managed Services in relation to the Go-Live Date (or the last of the Go-Live Dates if there is more than one), so that here is a single, coordinated end of the Term for the Managed Services.]</t>
+  </si>
+  <si>
+    <t>The methodology used to determine the potential elimination of a Service Level Credit, as described in Section 5 of Schedule B (Service Level Methodology).</t>
+  </si>
+  <si>
+    <t>[Twenty-five (25)] percentage points, which would represent [twenty-five percent (25%)] of the At Risk Amount.</t>
   </si>
 </sst>
 </file>
@@ -1666,20 +1666,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{265DBB42-7CE0-445D-BF3B-D3E1CB2564FA}">
   <dimension ref="B2:J96"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4" style="1" customWidth="1"/>
-    <col min="2" max="2" width="7.21875" style="14" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" style="14" customWidth="1"/>
+    <col min="2" max="2" width="7.1796875" style="14" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" style="14" customWidth="1"/>
     <col min="4" max="4" width="155" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="144.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="73.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="144.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="73.1796875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="10" width="45" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.21875" style="1"/>
+    <col min="11" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10" ht="29" x14ac:dyDescent="0.35">
       <c r="B2" s="10" t="s">
         <v>0</v>
       </c>
@@ -1705,10 +1705,10 @@
         <v>168</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B3" s="11">
         <v>1</v>
       </c>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="J3" s="4"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B4" s="11">
         <v>2</v>
       </c>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="J4" s="4"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B5" s="11">
         <v>3</v>
       </c>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="J5" s="4"/>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B6" s="11">
         <v>4</v>
       </c>
@@ -1790,7 +1790,7 @@
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B7" s="11">
         <v>5</v>
       </c>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="J7" s="4"/>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B8" s="11">
         <v>6</v>
       </c>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="J8" s="4"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B9" s="11">
         <v>7</v>
       </c>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="J9" s="4"/>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B10" s="11">
         <v>8</v>
       </c>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="J10" s="4"/>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B11" s="11">
         <v>9</v>
       </c>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="J11" s="4"/>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B12" s="11">
         <v>10</v>
       </c>
@@ -1916,7 +1916,7 @@
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
     </row>
-    <row r="13" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:10" ht="29" x14ac:dyDescent="0.35">
       <c r="B13" s="11">
         <v>11</v>
       </c>
@@ -1937,7 +1937,7 @@
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
       <c r="D14" s="4"/>
@@ -1948,7 +1948,7 @@
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B15" s="11">
         <v>12</v>
       </c>
@@ -1967,11 +1967,11 @@
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J15" s="4"/>
     </row>
-    <row r="16" spans="2:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:10" ht="58" x14ac:dyDescent="0.35">
       <c r="B16" s="11">
         <v>13</v>
       </c>
@@ -1990,11 +1990,11 @@
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J16" s="4"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
       <c r="D17" s="4"/>
@@ -2005,7 +2005,7 @@
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
     </row>
-    <row r="18" spans="2:10" ht="72" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="B18" s="11">
         <v>14</v>
       </c>
@@ -2024,11 +2024,11 @@
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J18" s="4"/>
     </row>
-    <row r="19" spans="2:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B19" s="11">
         <v>15</v>
       </c>
@@ -2049,7 +2049,7 @@
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
     </row>
-    <row r="20" spans="2:10" ht="72" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="B20" s="11">
         <v>16</v>
       </c>
@@ -2070,7 +2070,7 @@
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
     </row>
-    <row r="21" spans="2:10" ht="72" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="B21" s="11">
         <v>17</v>
       </c>
@@ -2078,7 +2078,7 @@
         <v>37</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>38</v>
@@ -2091,7 +2091,7 @@
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
     </row>
-    <row r="22" spans="2:10" ht="72" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="B22" s="11">
         <v>18</v>
       </c>
@@ -2112,7 +2112,7 @@
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
     </row>
-    <row r="23" spans="2:10" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:10" ht="116" x14ac:dyDescent="0.35">
       <c r="B23" s="11">
         <v>19</v>
       </c>
@@ -2133,7 +2133,7 @@
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
     </row>
-    <row r="24" spans="2:10" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:10" ht="159.5" x14ac:dyDescent="0.35">
       <c r="B24" s="11">
         <v>20</v>
       </c>
@@ -2154,7 +2154,7 @@
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
     </row>
-    <row r="25" spans="2:10" ht="149.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:10" ht="149.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="11">
         <v>21</v>
       </c>
@@ -2175,7 +2175,7 @@
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
     </row>
-    <row r="26" spans="2:10" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:10" ht="87" x14ac:dyDescent="0.35">
       <c r="B26" s="11">
         <v>22</v>
       </c>
@@ -2196,7 +2196,7 @@
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
     </row>
-    <row r="27" spans="2:10" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:10" ht="87" x14ac:dyDescent="0.35">
       <c r="B27" s="11">
         <v>23</v>
       </c>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="J27" s="4"/>
     </row>
-    <row r="28" spans="2:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="B28" s="11">
         <v>24</v>
       </c>
@@ -2240,7 +2240,7 @@
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
     </row>
-    <row r="29" spans="2:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B29" s="11">
         <v>25</v>
       </c>
@@ -2261,7 +2261,7 @@
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
     </row>
-    <row r="30" spans="2:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B30" s="11">
         <v>26</v>
       </c>
@@ -2282,7 +2282,7 @@
       <c r="I30" s="12"/>
       <c r="J30" s="12"/>
     </row>
-    <row r="31" spans="2:10" ht="72" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="B31" s="11">
         <v>27</v>
       </c>
@@ -2303,7 +2303,7 @@
       <c r="I31" s="12"/>
       <c r="J31" s="12"/>
     </row>
-    <row r="32" spans="2:10" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:10" ht="87" x14ac:dyDescent="0.35">
       <c r="B32" s="11">
         <v>28</v>
       </c>
@@ -2324,7 +2324,7 @@
       <c r="I32" s="12"/>
       <c r="J32" s="12"/>
     </row>
-    <row r="33" spans="2:10" ht="72" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="B33" s="11">
         <v>29</v>
       </c>
@@ -2345,7 +2345,7 @@
       <c r="I33" s="12"/>
       <c r="J33" s="12"/>
     </row>
-    <row r="34" spans="2:10" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:10" ht="87" x14ac:dyDescent="0.35">
       <c r="B34" s="11">
         <v>30</v>
       </c>
@@ -2366,7 +2366,7 @@
       <c r="I34" s="12"/>
       <c r="J34" s="12"/>
     </row>
-    <row r="35" spans="2:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B35" s="11">
         <v>31</v>
       </c>
@@ -2387,7 +2387,7 @@
       <c r="I35" s="12"/>
       <c r="J35" s="12"/>
     </row>
-    <row r="36" spans="2:10" ht="72" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="B36" s="11">
         <v>32</v>
       </c>
@@ -2408,7 +2408,7 @@
       <c r="I36" s="12"/>
       <c r="J36" s="12"/>
     </row>
-    <row r="37" spans="2:10" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:10" ht="87" x14ac:dyDescent="0.35">
       <c r="B37" s="11">
         <v>33</v>
       </c>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="J37" s="4"/>
     </row>
-    <row r="38" spans="2:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B38" s="11">
         <v>34</v>
       </c>
@@ -2452,7 +2452,7 @@
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
     </row>
-    <row r="39" spans="2:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B39" s="11">
         <v>35</v>
       </c>
@@ -2473,7 +2473,7 @@
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
     </row>
-    <row r="40" spans="2:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B40" s="11">
         <v>36</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>89</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>194</v>
+        <v>292</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>90</v>
@@ -2496,7 +2496,7 @@
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
     </row>
-    <row r="41" spans="2:10" ht="72" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="B41" s="11">
         <v>37</v>
       </c>
@@ -2517,7 +2517,7 @@
       <c r="I41" s="4"/>
       <c r="J41" s="4"/>
     </row>
-    <row r="42" spans="2:10" ht="72" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="B42" s="11">
         <v>38</v>
       </c>
@@ -2538,7 +2538,7 @@
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
     </row>
-    <row r="43" spans="2:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B43" s="11">
         <v>39</v>
       </c>
@@ -2559,7 +2559,7 @@
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B44" s="11">
         <v>40</v>
       </c>
@@ -2567,7 +2567,7 @@
         <v>104</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>105</v>
@@ -2580,7 +2580,7 @@
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
     </row>
-    <row r="45" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:10" ht="29" x14ac:dyDescent="0.35">
       <c r="B45" s="11">
         <v>41</v>
       </c>
@@ -2601,7 +2601,7 @@
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
     </row>
-    <row r="46" spans="2:10" ht="132" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:10" ht="125" x14ac:dyDescent="0.35">
       <c r="B46" s="11">
         <v>42</v>
       </c>
@@ -2609,20 +2609,20 @@
         <v>110</v>
       </c>
       <c r="D46" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F46" s="4"/>
       <c r="G46" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
       <c r="J46" s="24"/>
     </row>
-    <row r="47" spans="2:10" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:10" ht="159.5" x14ac:dyDescent="0.35">
       <c r="B47" s="11">
         <v>43</v>
       </c>
@@ -2643,7 +2643,7 @@
       <c r="I47" s="23"/>
       <c r="J47" s="22"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B48" s="11">
         <v>44</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>114</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>115</v>
@@ -2664,7 +2664,7 @@
       <c r="I48" s="23"/>
       <c r="J48" s="22"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B49" s="11">
         <v>45</v>
       </c>
@@ -2672,7 +2672,7 @@
         <v>117</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>118</v>
@@ -2685,18 +2685,18 @@
       <c r="I49" s="23"/>
       <c r="J49" s="22"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B50" s="11">
         <v>46</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D50" s="22" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E50" s="20" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F50" s="4"/>
       <c r="G50" s="4" t="s">
@@ -2709,10 +2709,10 @@
     <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="11"/>
       <c r="C51" s="19" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D51" s="28" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E51" s="27"/>
       <c r="F51" s="4"/>
@@ -2720,16 +2720,16 @@
       <c r="H51" s="4"/>
       <c r="I51" s="23"/>
       <c r="J51" s="22" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="11"/>
       <c r="C52" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="D52" s="28" t="s">
         <v>212</v>
-      </c>
-      <c r="D52" s="28" t="s">
-        <v>213</v>
       </c>
       <c r="E52" s="27"/>
       <c r="F52" s="4"/>
@@ -2737,16 +2737,16 @@
       <c r="H52" s="4"/>
       <c r="I52" s="23"/>
       <c r="J52" s="22" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="11"/>
       <c r="C53" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D53" s="28" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E53" s="27"/>
       <c r="F53" s="4"/>
@@ -2754,108 +2754,108 @@
       <c r="H53" s="4"/>
       <c r="I53" s="23"/>
       <c r="J53" s="22" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="54" spans="2:10" ht="43.2" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B54" s="11">
         <v>47</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D54" s="22" t="s">
+        <v>217</v>
+      </c>
+      <c r="E54" s="27" t="s">
         <v>218</v>
-      </c>
-      <c r="E54" s="27" t="s">
-        <v>219</v>
       </c>
       <c r="F54" s="4"/>
       <c r="G54" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H54" s="4"/>
       <c r="I54" s="23"/>
       <c r="J54" s="25" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B55" s="11">
         <v>48</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D55" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E55" s="27" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="27" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H55" s="4"/>
       <c r="I55" s="23"/>
       <c r="J55" s="25" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.3">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B56" s="11">
         <v>49</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D56" s="30" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E56" s="27" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F56" s="4"/>
       <c r="G56" s="27" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H56" s="4"/>
       <c r="I56" s="23"/>
       <c r="J56" s="25" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.3">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B57" s="11">
         <v>50</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D57" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="E57" s="27" t="s">
         <v>226</v>
-      </c>
-      <c r="E57" s="27" t="s">
-        <v>227</v>
       </c>
       <c r="F57" s="4"/>
       <c r="G57" s="27" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H57" s="4"/>
       <c r="I57" s="23"/>
       <c r="J57" s="25" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="58" spans="2:10" ht="43.2" x14ac:dyDescent="0.3">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B58" s="11"/>
       <c r="C58" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="D58" s="21" t="s">
         <v>200</v>
-      </c>
-      <c r="D58" s="21" t="s">
-        <v>201</v>
       </c>
       <c r="E58" s="4"/>
       <c r="F58" s="4"/>
@@ -2863,56 +2863,56 @@
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
       <c r="J58" s="25" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="59" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10" ht="29" x14ac:dyDescent="0.35">
       <c r="B59" s="11">
         <v>51</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F59" s="4"/>
       <c r="G59" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
       <c r="J59" s="25" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="60" spans="2:10" ht="43.2" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B60" s="11">
         <v>52</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>119</v>
       </c>
       <c r="F60" s="4"/>
       <c r="G60" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
       <c r="J60" s="25" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="61" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10" ht="29" x14ac:dyDescent="0.35">
       <c r="B61" s="11">
         <v>53</v>
       </c>
@@ -2932,15 +2932,15 @@
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
       <c r="J61" s="25" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="62" spans="2:10" ht="43.2" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B62" s="11">
         <v>54</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>124</v>
@@ -2955,10 +2955,10 @@
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
       <c r="J62" s="25" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="63" spans="2:10" ht="43.2" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="63" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B63" s="11">
         <v>55</v>
       </c>
@@ -2978,39 +2978,39 @@
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
       <c r="J63" s="25" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="64" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10" ht="29" x14ac:dyDescent="0.35">
       <c r="B64" s="11">
         <v>56</v>
       </c>
       <c r="C64" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="D64" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="D64" s="4" t="s">
+      <c r="E64" s="4" t="s">
         <v>238</v>
-      </c>
-      <c r="E64" s="4" t="s">
-        <v>239</v>
       </c>
       <c r="F64" s="4"/>
       <c r="G64" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H64" s="4"/>
       <c r="I64" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J64" s="25" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="65" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" ht="29" x14ac:dyDescent="0.35">
       <c r="B65" s="11"/>
       <c r="C65" s="11"/>
       <c r="D65" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
@@ -3018,14 +3018,14 @@
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
       <c r="J65" s="25" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="66" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" ht="29" x14ac:dyDescent="0.35">
       <c r="B66" s="11"/>
       <c r="C66" s="11"/>
       <c r="D66" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E66" s="4"/>
       <c r="F66" s="4"/>
@@ -3033,10 +3033,10 @@
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
       <c r="J66" s="25" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="67" spans="2:10" ht="43.2" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B67" s="11">
         <v>57</v>
       </c>
@@ -3044,7 +3044,7 @@
         <v>131</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E67" s="4" t="s">
         <v>132</v>
@@ -3056,10 +3056,10 @@
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
       <c r="J67" s="25" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="68" spans="2:10" ht="43.2" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B68" s="11">
         <v>58</v>
       </c>
@@ -3067,7 +3067,7 @@
         <v>134</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E68" s="4" t="s">
         <v>135</v>
@@ -3079,10 +3079,10 @@
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
       <c r="J68" s="25" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B69" s="11"/>
       <c r="C69" s="11"/>
       <c r="D69" s="4"/>
@@ -3093,18 +3093,18 @@
       <c r="I69" s="4"/>
       <c r="J69" s="26"/>
     </row>
-    <row r="70" spans="2:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B70" s="11">
         <v>59</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F70" s="4"/>
       <c r="G70" s="4" t="s">
@@ -3116,18 +3116,18 @@
       <c r="I70" s="4"/>
       <c r="J70" s="4"/>
     </row>
-    <row r="71" spans="2:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:10" ht="58" x14ac:dyDescent="0.35">
       <c r="B71" s="11">
         <v>60</v>
       </c>
       <c r="C71" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="D71" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="D71" s="4" t="s">
-        <v>289</v>
-      </c>
       <c r="E71" s="4" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="F71" s="4"/>
       <c r="G71" s="4" t="s">
@@ -3139,7 +3139,7 @@
       <c r="I71" s="4"/>
       <c r="J71" s="4"/>
     </row>
-    <row r="72" spans="2:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:10" ht="58" x14ac:dyDescent="0.35">
       <c r="B72" s="11">
         <v>61</v>
       </c>
@@ -3147,10 +3147,10 @@
         <v>140</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F72" s="4"/>
       <c r="G72" s="4" t="s">
@@ -3162,18 +3162,18 @@
       <c r="I72" s="4"/>
       <c r="J72" s="4"/>
     </row>
-    <row r="73" spans="2:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B73" s="11">
         <v>62</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F73" s="4"/>
       <c r="G73" s="4" t="s">
@@ -3185,13 +3185,13 @@
       <c r="I73" s="4"/>
       <c r="J73" s="4"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B74" s="11"/>
       <c r="C74" s="11" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>145</v>
@@ -3210,16 +3210,16 @@
         <v>24</v>
       </c>
     </row>
-    <row r="75" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:10" ht="29" x14ac:dyDescent="0.35">
       <c r="B75" s="11"/>
       <c r="C75" s="11" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>145</v>
@@ -3235,13 +3235,13 @@
         <v>24</v>
       </c>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B76" s="11"/>
       <c r="C76" s="11" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>147</v>
@@ -3260,262 +3260,262 @@
         <v>80</v>
       </c>
     </row>
-    <row r="77" spans="2:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:10" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B77" s="11"/>
       <c r="C77" s="11" t="s">
-        <v>294</v>
-      </c>
-      <c r="D77" s="9" t="s">
-        <v>259</v>
+        <v>291</v>
+      </c>
+      <c r="D77" s="31" t="s">
+        <v>257</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F77" s="4"/>
       <c r="G77" s="4"/>
       <c r="H77" s="4"/>
       <c r="I77" s="4"/>
       <c r="J77" s="4" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="78" spans="2:10" ht="26.4" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" ht="25" x14ac:dyDescent="0.25">
       <c r="C78" s="11" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D78" s="31" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F78" s="4"/>
       <c r="G78" s="4"/>
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
       <c r="J78" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="11"/>
       <c r="C79" s="11" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D79" s="29" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F79" s="4"/>
       <c r="G79" s="4"/>
       <c r="H79" s="4"/>
       <c r="I79" s="4"/>
       <c r="J79" s="4" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="80" spans="2:10" ht="26.4" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="11"/>
       <c r="C80" s="11" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D80" s="31" t="s">
-        <v>256</v>
+        <v>293</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F80" s="4"/>
       <c r="G80" s="4"/>
       <c r="H80" s="4"/>
       <c r="I80" s="4"/>
       <c r="J80" s="4" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="81" spans="2:10" ht="26.4" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10" ht="25" x14ac:dyDescent="0.25">
       <c r="B81" s="11"/>
       <c r="C81" s="11" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D81" s="31" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F81" s="4"/>
       <c r="G81" s="4"/>
       <c r="H81" s="4"/>
       <c r="I81" s="4"/>
       <c r="J81" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="11"/>
       <c r="C82" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="D82" s="31" t="s">
         <v>294</v>
       </c>
-      <c r="D82" s="31" t="s">
-        <v>262</v>
-      </c>
       <c r="E82" s="4" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F82" s="4"/>
       <c r="G82" s="4"/>
       <c r="H82" s="4"/>
       <c r="I82" s="4"/>
       <c r="J82" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="11"/>
       <c r="C83" s="11" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D83" s="31" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F83" s="4"/>
       <c r="G83" s="4"/>
       <c r="H83" s="4"/>
       <c r="I83" s="4"/>
       <c r="J83" s="4" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="84" spans="2:10" ht="26.4" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="84" spans="2:10" ht="25" x14ac:dyDescent="0.25">
       <c r="B84" s="11"/>
       <c r="C84" s="11" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D84" s="31" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F84" s="4"/>
       <c r="G84" s="4"/>
       <c r="H84" s="4"/>
       <c r="I84" s="4"/>
       <c r="J84" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="11"/>
       <c r="C85" s="11" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D85" s="31" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="F85" s="4"/>
       <c r="G85" s="4"/>
       <c r="H85" s="4"/>
       <c r="I85" s="4"/>
       <c r="J85" s="4" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="86" spans="2:10" ht="26.4" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10" ht="25" x14ac:dyDescent="0.25">
       <c r="B86" s="11"/>
       <c r="C86" s="11" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D86" s="31" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="F86" s="4"/>
       <c r="G86" s="4"/>
       <c r="H86" s="4"/>
       <c r="I86" s="4"/>
       <c r="J86" s="4" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="87" spans="2:10" ht="26.4" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10" ht="25" x14ac:dyDescent="0.25">
       <c r="B87" s="11"/>
       <c r="C87" s="11" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D87" s="31" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F87" s="4"/>
       <c r="G87" s="4"/>
       <c r="H87" s="4"/>
       <c r="I87" s="4"/>
       <c r="J87" s="4" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="88" spans="2:10" ht="26.4" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="88" spans="2:10" ht="25" x14ac:dyDescent="0.25">
       <c r="B88" s="11"/>
       <c r="C88" s="11" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D88" s="31" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F88" s="4"/>
       <c r="G88" s="4"/>
       <c r="H88" s="4"/>
       <c r="I88" s="4"/>
       <c r="J88" s="4" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="89" spans="2:10" ht="26.4" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="89" spans="2:10" ht="25" x14ac:dyDescent="0.25">
       <c r="B89" s="11"/>
       <c r="C89" s="11" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D89" s="31" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="F89" s="4"/>
       <c r="G89" s="4"/>
       <c r="H89" s="4"/>
       <c r="I89" s="4"/>
       <c r="J89" s="4" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="90" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="90" spans="2:10" ht="29" x14ac:dyDescent="0.35">
       <c r="B90" s="11"/>
       <c r="C90" s="11" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F90" s="4" t="s">
         <v>145</v>
@@ -3528,19 +3528,19 @@
       </c>
       <c r="I90" s="4"/>
       <c r="J90" s="4" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="91" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="91" spans="2:10" ht="29" x14ac:dyDescent="0.35">
       <c r="B91" s="11"/>
       <c r="C91" s="11" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F91" s="4"/>
       <c r="G91" s="4"/>
@@ -3550,16 +3550,16 @@
         <v>42</v>
       </c>
     </row>
-    <row r="92" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:10" ht="29" x14ac:dyDescent="0.35">
       <c r="B92" s="11"/>
       <c r="C92" s="11" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F92" s="4" t="s">
         <v>145</v>
@@ -3575,13 +3575,13 @@
         <v>42</v>
       </c>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B93" s="11"/>
       <c r="C93" s="11" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E93" s="4" t="s">
         <v>151</v>
@@ -3597,16 +3597,16 @@
       </c>
       <c r="I93" s="4"/>
       <c r="J93" s="4" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="94" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B94" s="11"/>
       <c r="C94" s="11" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E94" s="4" t="s">
         <v>153</v>
@@ -3622,10 +3622,10 @@
       </c>
       <c r="I94" s="4"/>
       <c r="J94" s="4" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="95" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B95" s="11"/>
       <c r="C95" s="11"/>
       <c r="D95" s="17"/>
@@ -3636,7 +3636,7 @@
       <c r="I95" s="4"/>
       <c r="J95" s="4"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B96" s="11"/>
       <c r="C96" s="11"/>
       <c r="D96" s="4"/>
@@ -3658,19 +3658,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F5AEE25-55E7-432F-AF5D-061A9E120231}">
   <dimension ref="B2:D9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="3.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="3.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C2" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B3" s="6" t="s">
         <v>156</v>
       </c>
@@ -3681,7 +3681,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B4" s="5">
         <v>1</v>
       </c>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="D4" s="8"/>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B5" s="5">
         <v>2</v>
       </c>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="D5" s="8"/>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B6" s="5">
         <v>3</v>
       </c>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="D6" s="8"/>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B7" s="5">
         <v>4</v>
       </c>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="D7" s="8"/>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C9" s="9" t="s">
         <v>160</v>
       </c>
@@ -3730,9 +3730,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0189E61E-37D7-4696-83EA-025EC3498A9D}">
   <dimension ref="B3:L7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="3" spans="2:12" ht="25.8" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:12" ht="26" x14ac:dyDescent="0.6">
       <c r="B3" s="15">
         <v>1</v>
       </c>
@@ -3749,7 +3749,7 @@
       <c r="K3" s="15"/>
       <c r="L3" s="15"/>
     </row>
-    <row r="4" spans="2:12" ht="25.8" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:12" ht="26" x14ac:dyDescent="0.6">
       <c r="B4" s="15">
         <v>2</v>
       </c>
@@ -3766,7 +3766,7 @@
       <c r="K4" s="15"/>
       <c r="L4" s="15"/>
     </row>
-    <row r="5" spans="2:12" ht="25.8" x14ac:dyDescent="0.5">
+    <row r="5" spans="2:12" ht="26" x14ac:dyDescent="0.6">
       <c r="B5" s="15">
         <v>3</v>
       </c>
@@ -3783,7 +3783,7 @@
       <c r="K5" s="15"/>
       <c r="L5" s="15"/>
     </row>
-    <row r="6" spans="2:12" ht="25.8" x14ac:dyDescent="0.5">
+    <row r="6" spans="2:12" ht="26" x14ac:dyDescent="0.6">
       <c r="B6" s="15">
         <v>4</v>
       </c>
@@ -3800,7 +3800,7 @@
       <c r="K6" s="15"/>
       <c r="L6" s="15"/>
     </row>
-    <row r="7" spans="2:12" ht="25.8" x14ac:dyDescent="0.5">
+    <row r="7" spans="2:12" ht="26" x14ac:dyDescent="0.6">
       <c r="B7" s="15">
         <v>5</v>
       </c>
